--- a/mgf_matched_5_guilds.xlsx
+++ b/mgf_matched_5_guilds.xlsx
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>376</t>
+    <t>377</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>121조 551억 8354만</t>
+    <t>125조 5532억 9483만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,90 +101,93 @@
     <t>망겜감별사</t>
   </si>
   <si>
+    <t>2026.04.10</t>
+  </si>
+  <si>
+    <t>피난민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>Scania 26</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>17위</t>
+  </si>
+  <si>
+    <t>137조 4077억 2612만</t>
+  </si>
+  <si>
+    <t>피난 오신 여러분 반갑습니다.</t>
+  </si>
+  <si>
+    <t>주방화</t>
+  </si>
+  <si>
+    <t>이고이스트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>135조 5251억 2923만</t>
+  </si>
+  <si>
+    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
+  </si>
+  <si>
+    <t>한도카드</t>
+  </si>
+  <si>
+    <t>부계둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>Lv.6</t>
+  </si>
+  <si>
+    <t>117조 1644억 9792만</t>
+  </si>
+  <si>
+    <t>부계들 + 부계둘</t>
+  </si>
+  <si>
+    <t>홍춘삼</t>
+  </si>
+  <si>
     <t>2026.04.09</t>
   </si>
   <si>
-    <t>피난민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>Scania 26</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>16위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>133조 2911억 1787만</t>
-  </si>
-  <si>
-    <t>피난 오신 여러분 반갑습니다.</t>
-  </si>
-  <si>
-    <t>주방화</t>
-  </si>
-  <si>
-    <t>이고이스트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>365</t>
-  </si>
-  <si>
-    <t>29위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>126조 7953억 4402만</t>
-  </si>
-  <si>
-    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
-  </si>
-  <si>
-    <t>한도카드</t>
-  </si>
-  <si>
-    <t>부계둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>117조 1644억 9792만</t>
-  </si>
-  <si>
-    <t>부계들 + 부계둘</t>
-  </si>
-  <si>
-    <t>홍춘삼</t>
-  </si>
-  <si>
     <t>밤과다람쥐</t>
   </si>
   <si>
@@ -194,16 +197,13 @@
     <t>Scania 5</t>
   </si>
   <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>12위</t>
+    <t>325</t>
   </si>
   <si>
     <t>28명</t>
   </si>
   <si>
-    <t>161조 5072억 2056만</t>
+    <t>171조 6333억 5023만</t>
   </si>
   <si>
     <t>자유가입 길드입니다 1d 길컨 미참 스펙상승에 따른 길컨 점수 미상향 추방컷 관리로 이루어지고 있습니다</t>
@@ -248,27 +248,30 @@
     <t>섀도어</t>
   </si>
   <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>15조 258억 4050만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>큐샤프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>15조 258억 4050만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>큐샤프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
     <t>14조 951억 2182만</t>
   </si>
   <si>
@@ -302,7 +305,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>9조 1292억 4934만</t>
+    <t>9조 2433억 4747만</t>
   </si>
   <si>
     <t>5</t>
@@ -557,7 +560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1조 7375억 5453만</t>
+    <t>1조 7445억 1884만</t>
   </si>
   <si>
     <t>24</t>
@@ -935,9 +938,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
     <t>39조 7974억 3406만</t>
   </si>
   <si>
@@ -1466,7 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=MAKTO</t>
   </si>
   <si>
-    <t>83조 6525억 7140만</t>
+    <t>84조 1898억 3942만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
@@ -1661,7 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
   </si>
   <si>
-    <t>2252억 4262만</t>
+    <t>2258억 9094만</t>
   </si>
   <si>
     <t>우주강아지</t>
@@ -1700,7 +1700,7 @@
     <t>86</t>
   </si>
   <si>
-    <t>591억 5747만</t>
+    <t>647억 8326만</t>
   </si>
   <si>
     <t>만년설딸기</t>
@@ -2199,16 +2199,16 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2216,31 +2216,31 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>40</v>
@@ -2293,33 +2293,33 @@
         <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>57</v>
@@ -2452,10 +2452,10 @@
         <v>79</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2466,28 +2466,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2498,28 +2498,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2530,28 +2530,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2562,28 +2562,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2594,28 +2594,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2626,28 +2626,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2658,16 +2658,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>78</v>
@@ -2676,10 +2676,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2690,28 +2690,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2722,28 +2722,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2754,28 +2754,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2786,16 +2786,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>78</v>
@@ -2804,10 +2804,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2818,28 +2818,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2850,28 +2850,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2882,28 +2882,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2914,16 +2914,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>78</v>
@@ -2932,10 +2932,10 @@
         <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2946,28 +2946,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2978,16 +2978,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>78</v>
@@ -2996,10 +2996,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3010,16 +3010,16 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>78</v>
@@ -3028,10 +3028,10 @@
         <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3042,16 +3042,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>78</v>
@@ -3060,10 +3060,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3074,16 +3074,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>78</v>
@@ -3092,10 +3092,10 @@
         <v>79</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3106,28 +3106,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3138,28 +3138,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3170,16 +3170,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>78</v>
@@ -3188,10 +3188,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3202,28 +3202,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3234,16 +3234,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>78</v>
@@ -3252,10 +3252,10 @@
         <v>79</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3266,16 +3266,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>78</v>
@@ -3284,10 +3284,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3298,16 +3298,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>78</v>
@@ -3316,10 +3316,10 @@
         <v>72</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3417,13 +3417,13 @@
         <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>78</v>
@@ -3432,10 +3432,10 @@
         <v>79</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3449,25 +3449,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3478,16 +3478,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>78</v>
@@ -3496,10 +3496,10 @@
         <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3510,16 +3510,16 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>78</v>
@@ -3528,10 +3528,10 @@
         <v>79</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3542,28 +3542,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3574,28 +3574,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3606,28 +3606,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3638,28 +3638,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3670,28 +3670,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3702,16 +3702,16 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
@@ -3720,10 +3720,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3734,28 +3734,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3766,16 +3766,16 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>78</v>
@@ -3784,10 +3784,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3798,16 +3798,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>78</v>
@@ -3816,10 +3816,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3830,28 +3830,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3862,28 +3862,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3894,28 +3894,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3926,28 +3926,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3958,16 +3958,16 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>78</v>
@@ -3976,10 +3976,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3990,28 +3990,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4022,28 +4022,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4054,16 +4054,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>78</v>
@@ -4072,10 +4072,10 @@
         <v>79</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4086,28 +4086,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4118,28 +4118,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4150,16 +4150,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>78</v>
@@ -4168,10 +4168,10 @@
         <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4182,16 +4182,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>78</v>
@@ -4200,10 +4200,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4214,28 +4214,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4246,16 +4246,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>78</v>
@@ -4264,10 +4264,10 @@
         <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4278,16 +4278,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>78</v>
@@ -4296,10 +4296,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4310,28 +4310,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4342,28 +4342,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4456,28 +4456,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>303</v>
@@ -4488,7 +4488,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
@@ -4509,7 +4509,7 @@
         <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>306</v>
@@ -4520,10 +4520,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>307</v>
@@ -4538,10 +4538,10 @@
         <v>78</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>309</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>310</v>
@@ -4573,7 +4573,7 @@
         <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>312</v>
@@ -4584,10 +4584,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>313</v>
@@ -4602,10 +4602,10 @@
         <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>315</v>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>316</v>
@@ -4634,10 +4634,10 @@
         <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>318</v>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>42</v>
@@ -4669,7 +4669,7 @@
         <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>320</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>321</v>
@@ -4698,10 +4698,10 @@
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>323</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -4730,10 +4730,10 @@
         <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>326</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>327</v>
@@ -4765,7 +4765,7 @@
         <v>79</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>329</v>
@@ -4776,10 +4776,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>330</v>
@@ -4797,7 +4797,7 @@
         <v>72</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>332</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>333</v>
@@ -4829,7 +4829,7 @@
         <v>79</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>335</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>336</v>
@@ -4858,10 +4858,10 @@
         <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>338</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>339</v>
@@ -4893,7 +4893,7 @@
         <v>79</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>341</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>342</v>
@@ -4925,7 +4925,7 @@
         <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>344</v>
@@ -4936,10 +4936,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>345</v>
@@ -4957,7 +4957,7 @@
         <v>79</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>347</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>348</v>
@@ -4989,7 +4989,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>350</v>
@@ -5000,10 +5000,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>351</v>
@@ -5018,10 +5018,10 @@
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>353</v>
@@ -5032,10 +5032,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>354</v>
@@ -5050,10 +5050,10 @@
         <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>356</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>357</v>
@@ -5085,7 +5085,7 @@
         <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>359</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>360</v>
@@ -5114,10 +5114,10 @@
         <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>362</v>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>363</v>
@@ -5149,7 +5149,7 @@
         <v>79</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>365</v>
@@ -5160,10 +5160,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>366</v>
@@ -5181,7 +5181,7 @@
         <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>368</v>
@@ -5192,10 +5192,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>369</v>
@@ -5210,10 +5210,10 @@
         <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>371</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>372</v>
@@ -5242,10 +5242,10 @@
         <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>374</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>375</v>
@@ -5274,10 +5274,10 @@
         <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>377</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>378</v>
@@ -5309,7 +5309,7 @@
         <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>380</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>381</v>
@@ -5338,10 +5338,10 @@
         <v>78</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>383</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>384</v>
@@ -5370,10 +5370,10 @@
         <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>386</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>387</v>
@@ -5405,7 +5405,7 @@
         <v>72</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>389</v>
@@ -5519,16 +5519,16 @@
         <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>392</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5551,16 +5551,16 @@
         <v>78</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>395</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5568,7 +5568,7 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>396</v>
@@ -5586,13 +5586,13 @@
         <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>398</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5600,7 +5600,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>399</v>
@@ -5618,13 +5618,13 @@
         <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>401</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5632,7 +5632,7 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>402</v>
@@ -5650,13 +5650,13 @@
         <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5664,7 +5664,7 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>405</v>
@@ -5682,13 +5682,13 @@
         <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>407</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5696,7 +5696,7 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>408</v>
@@ -5711,16 +5711,16 @@
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>410</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5728,7 +5728,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>411</v>
@@ -5743,16 +5743,16 @@
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>413</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5760,7 +5760,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>414</v>
@@ -5775,16 +5775,16 @@
         <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>416</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5792,7 +5792,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>417</v>
@@ -5810,13 +5810,13 @@
         <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>419</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5824,7 +5824,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>420</v>
@@ -5839,16 +5839,16 @@
         <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>422</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5856,7 +5856,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>423</v>
@@ -5874,13 +5874,13 @@
         <v>79</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>425</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5888,7 +5888,7 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>426</v>
@@ -5903,16 +5903,16 @@
         <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>428</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5920,7 +5920,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>429</v>
@@ -5938,13 +5938,13 @@
         <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>431</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5952,7 +5952,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>432</v>
@@ -5970,13 +5970,13 @@
         <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>434</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -5984,7 +5984,7 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>435</v>
@@ -5999,16 +5999,16 @@
         <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>437</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6016,7 +6016,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>438</v>
@@ -6031,16 +6031,16 @@
         <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>440</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6048,7 +6048,7 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>441</v>
@@ -6063,16 +6063,16 @@
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>443</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6080,7 +6080,7 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>444</v>
@@ -6098,13 +6098,13 @@
         <v>79</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>446</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6112,7 +6112,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>447</v>
@@ -6127,16 +6127,16 @@
         <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>449</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6144,7 +6144,7 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>450</v>
@@ -6159,16 +6159,16 @@
         <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>452</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6176,7 +6176,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>453</v>
@@ -6191,16 +6191,16 @@
         <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>455</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6208,7 +6208,7 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>456</v>
@@ -6223,16 +6223,16 @@
         <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>458</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6240,7 +6240,7 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>459</v>
@@ -6255,16 +6255,16 @@
         <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>461</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6272,7 +6272,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>51</v>
@@ -6287,16 +6287,16 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>463</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6304,7 +6304,7 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>464</v>
@@ -6322,13 +6322,13 @@
         <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>466</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6336,7 +6336,7 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>467</v>
@@ -6354,13 +6354,13 @@
         <v>79</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>469</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6368,7 +6368,7 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>470</v>
@@ -6383,16 +6383,16 @@
         <v>78</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>472</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6400,7 +6400,7 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>473</v>
@@ -6415,7 +6415,7 @@
         <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>475</v>
@@ -6424,7 +6424,7 @@
         <v>476</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>69</v>
@@ -6534,7 +6534,7 @@
         <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>479</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
@@ -6566,7 +6566,7 @@
         <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>481</v>
@@ -6577,10 +6577,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>482</v>
@@ -6598,7 +6598,7 @@
         <v>79</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>484</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>485</v>
@@ -6630,7 +6630,7 @@
         <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>487</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>488</v>
@@ -6662,7 +6662,7 @@
         <v>79</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>490</v>
@@ -6673,10 +6673,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>491</v>
@@ -6691,10 +6691,10 @@
         <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>493</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>494</v>
@@ -6723,10 +6723,10 @@
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>496</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>497</v>
@@ -6758,7 +6758,7 @@
         <v>72</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>499</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>500</v>
@@ -6787,10 +6787,10 @@
         <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>502</v>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>503</v>
@@ -6822,7 +6822,7 @@
         <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>505</v>
@@ -6833,10 +6833,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>506</v>
@@ -6851,10 +6851,10 @@
         <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>508</v>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>509</v>
@@ -6886,7 +6886,7 @@
         <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>511</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>512</v>
@@ -6915,10 +6915,10 @@
         <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>514</v>
@@ -6929,10 +6929,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>515</v>
@@ -6950,7 +6950,7 @@
         <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>517</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>518</v>
@@ -6982,7 +6982,7 @@
         <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>520</v>
@@ -6993,10 +6993,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>521</v>
@@ -7014,7 +7014,7 @@
         <v>79</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>523</v>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>524</v>
@@ -7046,7 +7046,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>526</v>
@@ -7057,10 +7057,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>527</v>
@@ -7075,10 +7075,10 @@
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>529</v>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>530</v>
@@ -7107,10 +7107,10 @@
         <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>532</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>533</v>
@@ -7139,10 +7139,10 @@
         <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>535</v>
@@ -7153,10 +7153,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>536</v>
@@ -7174,7 +7174,7 @@
         <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>538</v>
@@ -7185,10 +7185,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>539</v>
@@ -7203,10 +7203,10 @@
         <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>541</v>
@@ -7217,10 +7217,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>542</v>
@@ -7235,10 +7235,10 @@
         <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>544</v>
@@ -7249,10 +7249,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>545</v>
@@ -7270,7 +7270,7 @@
         <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>547</v>
@@ -7281,10 +7281,10 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>548</v>
@@ -7299,10 +7299,10 @@
         <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>550</v>
@@ -7313,10 +7313,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>551</v>
@@ -7331,10 +7331,10 @@
         <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>553</v>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>554</v>
@@ -7377,10 +7377,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>558</v>
@@ -7395,7 +7395,7 @@
         <v>78</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>560</v>

--- a/mgf_matched_5_guilds.xlsx
+++ b/mgf_matched_5_guilds.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="561">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>377</t>
+    <t>376</t>
   </si>
   <si>
     <t>13위</t>
@@ -113,7 +113,7 @@
     <t>Scania 26</t>
   </si>
   <si>
-    <t>361</t>
+    <t>362</t>
   </si>
   <si>
     <t>17위</t>
@@ -167,7 +167,7 @@
     <t>Scania 29</t>
   </si>
   <si>
-    <t>389</t>
+    <t>378</t>
   </si>
   <si>
     <t>10위</t>
@@ -176,7 +176,7 @@
     <t>Lv.6</t>
   </si>
   <si>
-    <t>117조 1644억 9792만</t>
+    <t>124조 4701억 3596만</t>
   </si>
   <si>
     <t>부계들 + 부계둘</t>
@@ -185,9 +185,6 @@
     <t>홍춘삼</t>
   </si>
   <si>
-    <t>2026.04.09</t>
-  </si>
-  <si>
     <t>밤과다람쥐</t>
   </si>
   <si>
@@ -197,7 +194,7 @@
     <t>Scania 5</t>
   </si>
   <si>
-    <t>325</t>
+    <t>324</t>
   </si>
   <si>
     <t>28명</t>
@@ -839,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%88%98%EB%8F%BC%EC%A7%80%EB%A1%9C%EC%84%B1</t>
   </si>
   <si>
-    <t>4725억 7338만</t>
+    <t>4736억 918만</t>
   </si>
   <si>
     <t>딱지냥</t>
@@ -869,7 +866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
   </si>
   <si>
-    <t>1747억 4190만</t>
+    <t>1750억 8049만</t>
   </si>
   <si>
     <t>샾갈배</t>
@@ -965,7 +962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B8%88%EA%B8%B0</t>
   </si>
   <si>
-    <t>10조 8604억 7188만</t>
+    <t>11조 3968억 6209만</t>
   </si>
   <si>
     <t>환불카드</t>
@@ -983,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>5조 9895억 3647만</t>
+    <t>6조 1023억 6033만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
@@ -1043,7 +1040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
   </si>
   <si>
-    <t>1조 629억 6032만</t>
+    <t>1조 1014억 1022만</t>
   </si>
   <si>
     <t>망치전문</t>
@@ -1052,7 +1049,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
   </si>
   <si>
-    <t>1조 322억 4092만</t>
+    <t>1조 927억 6855만</t>
   </si>
   <si>
     <t>핑와스</t>
@@ -1064,6 +1061,15 @@
     <t>8953억 4884만</t>
   </si>
   <si>
+    <t>호츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>8232억 647만</t>
+  </si>
+  <si>
     <t>돌격대원</t>
   </si>
   <si>
@@ -1082,13 +1088,13 @@
     <t>8061억 7543만</t>
   </si>
   <si>
-    <t>호츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>8060억 1657만</t>
+    <t>비숍덩구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>7662억 1359만</t>
   </si>
   <si>
     <t>단풍a</t>
@@ -1109,15 +1115,6 @@
     <t>7185억 5363만</t>
   </si>
   <si>
-    <t>비숍덩구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>7175억 5362만</t>
-  </si>
-  <si>
     <t>회원카드</t>
   </si>
   <si>
@@ -1142,7 +1139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
   </si>
   <si>
-    <t>6723억 3651만</t>
+    <t>6737억 7585만</t>
   </si>
   <si>
     <t>로우머</t>
@@ -1244,6 +1241,15 @@
     <t>9조 2454억 5199만</t>
   </si>
   <si>
+    <t>처히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
+  </si>
+  <si>
+    <t>9조 2055억 8485만</t>
+  </si>
+  <si>
     <t>밍진</t>
   </si>
   <si>
@@ -1253,15 +1259,6 @@
     <t>8조 9166억 6911만</t>
   </si>
   <si>
-    <t>처히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
-  </si>
-  <si>
-    <t>7조 6221억 9029만</t>
-  </si>
-  <si>
     <t>Naco</t>
   </si>
   <si>
@@ -1295,7 +1292,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
   </si>
   <si>
-    <t>2조 9219억 4210만</t>
+    <t>3조 4240억 573만</t>
+  </si>
+  <si>
+    <t>천칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>2조 6405억 2496만</t>
   </si>
   <si>
     <t>토미오카상</t>
@@ -1307,15 +1313,6 @@
     <t>2조 4729억 2531만</t>
   </si>
   <si>
-    <t>천칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>2조 3744억 4175만</t>
-  </si>
-  <si>
     <t>평평이형</t>
   </si>
   <si>
@@ -1427,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=Targa</t>
   </si>
   <si>
-    <t>5188억 1533만</t>
+    <t>5228억 2157만</t>
   </si>
   <si>
     <t>애둘이에요</t>
@@ -2293,27 +2290,27 @@
         <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
@@ -2322,16 +2319,16 @@
         <v>38</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2370,28 +2367,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2402,7 +2399,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -2411,19 +2408,19 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2434,28 +2431,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2466,28 +2463,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2498,28 +2495,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2530,28 +2527,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2562,28 +2559,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2594,28 +2591,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2626,28 +2623,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2658,28 +2655,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2690,28 +2687,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2722,28 +2719,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2754,28 +2751,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2786,28 +2783,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2818,28 +2815,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2850,28 +2847,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2882,28 +2879,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2914,28 +2911,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2946,28 +2943,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2978,28 +2975,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3010,28 +3007,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3042,28 +3039,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3074,28 +3071,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3106,28 +3103,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3138,28 +3135,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3170,28 +3167,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3202,28 +3199,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3234,28 +3231,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3266,28 +3263,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3298,28 +3295,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3382,28 +3379,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3414,28 +3411,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3446,28 +3443,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3478,28 +3475,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3510,28 +3507,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3542,28 +3539,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3574,28 +3571,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3606,28 +3603,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3638,28 +3635,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3670,28 +3667,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3702,28 +3699,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3734,7 +3731,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
@@ -3743,19 +3740,19 @@
         <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3766,28 +3763,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3798,28 +3795,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3830,28 +3827,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3862,28 +3859,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3894,28 +3891,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3926,28 +3923,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3958,28 +3955,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3990,28 +3987,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4022,28 +4019,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4054,28 +4051,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4086,28 +4083,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4118,28 +4115,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4150,28 +4147,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4182,28 +4179,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4214,28 +4211,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4246,28 +4243,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4278,28 +4275,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4310,28 +4307,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4342,28 +4339,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4427,28 +4424,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4459,28 +4456,28 @@
         <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4491,28 +4488,28 @@
         <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4523,28 +4520,28 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4555,28 +4552,28 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4587,28 +4584,28 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4619,28 +4616,28 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4651,7 +4648,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>42</v>
@@ -4660,19 +4657,19 @@
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4683,28 +4680,28 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4715,28 +4712,28 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4747,28 +4744,28 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4779,28 +4776,28 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4811,28 +4808,28 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4843,28 +4840,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4875,28 +4872,28 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4907,28 +4904,28 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4939,28 +4936,28 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4971,28 +4968,28 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5003,28 +5000,28 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5035,28 +5032,28 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5067,28 +5064,28 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5099,28 +5096,28 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5131,28 +5128,28 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5163,28 +5160,28 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5195,28 +5192,28 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5227,28 +5224,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5259,28 +5256,28 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5291,28 +5288,28 @@
         <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5323,28 +5320,28 @@
         <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5355,28 +5352,28 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5387,28 +5384,28 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5472,28 +5469,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5504,31 +5501,31 @@
         <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5536,31 +5533,31 @@
         <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>395</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5568,31 +5565,31 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5600,31 +5597,31 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5632,31 +5629,31 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5664,31 +5661,31 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5696,31 +5693,31 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5728,31 +5725,31 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>413</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5760,31 +5757,31 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5792,31 +5789,31 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>419</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5824,31 +5821,31 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5856,31 +5853,31 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5888,31 +5885,31 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5920,31 +5917,31 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5952,31 +5949,31 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -5984,31 +5981,31 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6016,31 +6013,31 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>440</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6048,31 +6045,31 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>443</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6080,31 +6077,31 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6112,31 +6109,31 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>449</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6144,31 +6141,31 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>452</v>
-      </c>
       <c r="J22" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6176,31 +6173,31 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>455</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6208,31 +6205,31 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>458</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6240,31 +6237,31 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>461</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6272,7 +6269,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>51</v>
@@ -6281,22 +6278,22 @@
         <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>463</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6304,31 +6301,31 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6336,31 +6333,31 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6368,31 +6365,31 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6400,31 +6397,31 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6484,28 +6481,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6513,31 +6510,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6545,31 +6542,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6577,31 +6574,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6609,31 +6606,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6641,31 +6638,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6673,31 +6670,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6705,31 +6702,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6737,31 +6734,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6769,31 +6766,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6801,31 +6798,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6833,31 +6830,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6865,31 +6862,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6897,31 +6894,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6929,31 +6926,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6961,31 +6958,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6993,31 +6990,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7025,31 +7022,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7057,31 +7054,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7089,31 +7086,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7121,31 +7118,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7153,31 +7150,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7185,31 +7182,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7217,31 +7214,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7249,31 +7246,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7281,31 +7278,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7313,31 +7310,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7345,31 +7342,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7377,31 +7374,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>

--- a/mgf_matched_5_guilds.xlsx
+++ b/mgf_matched_5_guilds.xlsx
@@ -377,7 +377,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 8502억 4550만</t>
+    <t>4조 8514억 8991만</t>
   </si>
   <si>
     <t>10</t>
@@ -404,7 +404,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>3조 4856억 5370만</t>
+    <t>3조 4930억 3221만</t>
   </si>
   <si>
     <t>12</t>
@@ -1469,7 +1469,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
   </si>
   <si>
-    <t>47조 8744억 1142만</t>
+    <t>47조 8894억 2761만</t>
   </si>
   <si>
     <t>민헤</t>
@@ -1478,7 +1478,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%97%A4</t>
   </si>
   <si>
-    <t>11조 2585억 1755만</t>
+    <t>11조 5168억 7356만</t>
   </si>
   <si>
     <t>세계챔피언</t>
@@ -1514,7 +1514,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
   </si>
   <si>
-    <t>1조 9107억 1607만</t>
+    <t>1조 9230억 4486만</t>
   </si>
   <si>
     <t>보꿍</t>
@@ -1709,7 +1709,7 @@
     <t>83</t>
   </si>
   <si>
-    <t>128억 9781만</t>
+    <t>131억 9115만</t>
   </si>
 </sst>
 </file>

--- a/mgf_matched_5_guilds.xlsx
+++ b/mgf_matched_5_guilds.xlsx
@@ -731,7 +731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%B0%A9%ED%99%94</t>
   </si>
   <si>
-    <t>2조 1943억 8459만</t>
+    <t>2조 3354억 9574만</t>
   </si>
   <si>
     <t>샾오산</t>
@@ -806,7 +806,7 @@
     <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
   </si>
   <si>
-    <t>1조 2643억 9879만</t>
+    <t>1조 3260억 7678만</t>
   </si>
   <si>
     <t>샾햇살</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
   </si>
   <si>
-    <t>3842억 3379만</t>
+    <t>3926억 8648만</t>
   </si>
   <si>
     <t>샾영세</t>
@@ -866,7 +866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
   </si>
   <si>
-    <t>1750억 8049만</t>
+    <t>1822억 4872만</t>
   </si>
   <si>
     <t>샾갈배</t>

--- a/mgf_matched_5_guilds.xlsx
+++ b/mgf_matched_5_guilds.xlsx
@@ -980,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>6조 1023억 6033만</t>
+    <t>6조 1256억 7831만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
@@ -1040,7 +1040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
   </si>
   <si>
-    <t>1조 1014억 1022만</t>
+    <t>1조 1551억 3755만</t>
   </si>
   <si>
     <t>망치전문</t>
@@ -1124,6 +1124,15 @@
     <t>7126억 7783만</t>
   </si>
   <si>
+    <t>떼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>6842억 7643만</t>
+  </si>
+  <si>
     <t>오보기다</t>
   </si>
   <si>
@@ -1133,15 +1142,6 @@
     <t>6741억 7723만</t>
   </si>
   <si>
-    <t>떼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>6737억 7585만</t>
-  </si>
-  <si>
     <t>로우머</t>
   </si>
   <si>
@@ -1202,7 +1202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
   </si>
   <si>
-    <t>17조 214억 6850만</t>
+    <t>17조 777억 7587만</t>
   </si>
   <si>
     <t>둥둥콩이</t>
@@ -1232,6 +1232,15 @@
     <t>11조 1534억 3734만</t>
   </si>
   <si>
+    <t>처히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
+  </si>
+  <si>
+    <t>9조 3395억 1763만</t>
+  </si>
+  <si>
     <t>환생의불꼬츠</t>
   </si>
   <si>
@@ -1241,15 +1250,6 @@
     <t>9조 2454억 5199만</t>
   </si>
   <si>
-    <t>처히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
-  </si>
-  <si>
-    <t>9조 2055억 8485만</t>
-  </si>
-  <si>
     <t>밍진</t>
   </si>
   <si>
@@ -1265,7 +1265,7 @@
     <t>https://mgf.gg/contents/character.php?n=Naco</t>
   </si>
   <si>
-    <t>6조 1505억 7520만</t>
+    <t>6조 6735억 7182만</t>
   </si>
   <si>
     <t>AKPS</t>
@@ -1310,7 +1310,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
   </si>
   <si>
-    <t>2조 4729억 2531만</t>
+    <t>2조 5102억 2762만</t>
   </si>
   <si>
     <t>평평이형</t>
@@ -1364,7 +1364,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
   </si>
   <si>
-    <t>1조 5976억 7853만</t>
+    <t>1조 6522억 7711만</t>
   </si>
   <si>
     <t>샤스찌에</t>
@@ -1454,7 +1454,7 @@
     <t>80</t>
   </si>
   <si>
-    <t>51억 7641만</t>
+    <t>51억 8649만</t>
   </si>
   <si>
     <t>MAKTO</t>
@@ -5175,10 +5175,10 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>146</v>
+        <v>265</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>367</v>
@@ -5207,10 +5207,10 @@
         <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>265</v>
+        <v>146</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>370</v>
@@ -5644,7 +5644,7 @@
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>85</v>
@@ -5676,7 +5676,7 @@
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>85</v>
@@ -5743,7 +5743,7 @@
         <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>412</v>
@@ -5903,7 +5903,7 @@
         <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>427</v>
